--- a/de.bund.bfr.knime.openkrise.db/src/de/bund/bfr/knime/openkrise/db/imports/custom/bfrnewformat/FCL_Backtrace_Prod_de.xlsx
+++ b/de.bund.bfr.knime.openkrise.db/src/de/bund/bfr/knime/openkrise/db/imports/custom/bfrnewformat/FCL_Backtrace_Prod_de.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24332"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C101CCB-C37C-438C-AC83-7A7F80FEF94E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="68" yWindow="5408" windowWidth="25215" windowHeight="5745"/>
+    <workbookView xWindow="1005" yWindow="1995" windowWidth="28695" windowHeight="15075" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Herstellung - Rückverfolgung" sheetId="5" r:id="rId1"/>
@@ -12,7 +13,18 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Herstellung - Rückverfolgung'!$A$1:$M$39</definedName>
   </definedNames>
-  <calcPr calcId="145621"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -124,16 +136,16 @@
     <t>Anzufragender Betrieb:</t>
   </si>
   <si>
-    <t>Bei Rückfragen bitte einfach Kontakt aufnehmen mit dem BfR FoodRiskLabs-Team, +49 (30) 18412-4444, foodrisklabs@bfr.bund.de</t>
+    <t>Bei Rückfragen bitte das BfR FoodRiskLabs-Team per E-Mail kontaktieren: foodrisklabs@bfr.bund.de</t>
   </si>
   <si>
-    <t>Digitale Auszüge (z.B. Excel oder xml-Dateien) vom befragten Betrieb könnten ebenso geeignet sein; das Ausfüllen dieser Vorlage wäre dann nicht notwendig - für diesen Fall bitte Rückruf (BfR FoodRiskLabs-Team, +49 (30) 18412-4444)</t>
+    <t>Digitale Auszüge (z.B. Excel oder xml-Dateien) vom befragten Betrieb könnten ebenso geeignet sein; das Ausfüllen dieser Vorlage wäre dann nicht notwendig - für diesen Fall kontaktieren Sie uns bitte.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="41" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1418,120 +1430,120 @@
     </xf>
   </cellXfs>
   <cellStyles count="114">
-    <cellStyle name="20% - Accent1 2" xfId="4"/>
-    <cellStyle name="20% - Accent2 2" xfId="5"/>
-    <cellStyle name="20% - Accent3 2" xfId="6"/>
-    <cellStyle name="20% - Accent4 2" xfId="7"/>
-    <cellStyle name="20% - Accent5 2" xfId="8"/>
-    <cellStyle name="20% - Accent6 2" xfId="9"/>
-    <cellStyle name="40% - Accent1 2" xfId="10"/>
-    <cellStyle name="40% - Accent2 2" xfId="11"/>
-    <cellStyle name="40% - Accent3 2" xfId="12"/>
-    <cellStyle name="40% - Accent4 2" xfId="13"/>
-    <cellStyle name="40% - Accent5 2" xfId="14"/>
-    <cellStyle name="40% - Accent6 2" xfId="15"/>
-    <cellStyle name="60% - Accent1 2" xfId="16"/>
-    <cellStyle name="60% - Accent2 2" xfId="17"/>
-    <cellStyle name="60% - Accent3 2" xfId="18"/>
-    <cellStyle name="60% - Accent4 2" xfId="19"/>
-    <cellStyle name="60% - Accent5 2" xfId="20"/>
-    <cellStyle name="60% - Accent6 2" xfId="21"/>
-    <cellStyle name="Accent1 2" xfId="22"/>
-    <cellStyle name="Accent2 2" xfId="23"/>
-    <cellStyle name="Accent3 2" xfId="24"/>
-    <cellStyle name="Accent4 2" xfId="25"/>
-    <cellStyle name="Accent5 2" xfId="26"/>
-    <cellStyle name="Accent6 2" xfId="27"/>
-    <cellStyle name="Bad 2" xfId="28"/>
-    <cellStyle name="Calculation 2" xfId="29"/>
-    <cellStyle name="Check Cell 2" xfId="30"/>
-    <cellStyle name="Explanatory Text 2" xfId="31"/>
-    <cellStyle name="Good 2" xfId="32"/>
-    <cellStyle name="Heading 1 2" xfId="33"/>
-    <cellStyle name="Heading 2 2" xfId="34"/>
-    <cellStyle name="Heading 3 2" xfId="35"/>
-    <cellStyle name="Heading 4 2" xfId="36"/>
-    <cellStyle name="Input 2" xfId="37"/>
-    <cellStyle name="Linked Cell 2" xfId="38"/>
-    <cellStyle name="Neutral 2" xfId="39"/>
-    <cellStyle name="Normal 10" xfId="40"/>
-    <cellStyle name="Normal 10 2" xfId="41"/>
-    <cellStyle name="Normal 10 2 2" xfId="42"/>
-    <cellStyle name="Normal 10 2 3" xfId="43"/>
-    <cellStyle name="Normal 10 3" xfId="44"/>
-    <cellStyle name="Normal 10 4" xfId="45"/>
-    <cellStyle name="Normal 11" xfId="46"/>
-    <cellStyle name="Normal 11 2" xfId="47"/>
-    <cellStyle name="Normal 11 2 2" xfId="48"/>
-    <cellStyle name="Normal 11 2 3" xfId="49"/>
-    <cellStyle name="Normal 11 3" xfId="50"/>
-    <cellStyle name="Normal 11 4" xfId="51"/>
-    <cellStyle name="Normal 12" xfId="52"/>
-    <cellStyle name="Normal 12 2" xfId="53"/>
-    <cellStyle name="Normal 12 3" xfId="54"/>
-    <cellStyle name="Normal 12 4" xfId="55"/>
-    <cellStyle name="Normal 13" xfId="56"/>
-    <cellStyle name="Normal 13 2" xfId="57"/>
-    <cellStyle name="Normal 13 3" xfId="58"/>
-    <cellStyle name="Normal 13 4" xfId="59"/>
-    <cellStyle name="Normal 14" xfId="60"/>
-    <cellStyle name="Normal 14 2" xfId="61"/>
-    <cellStyle name="Normal 15" xfId="62"/>
-    <cellStyle name="Normal 15 2" xfId="63"/>
-    <cellStyle name="Normal 16" xfId="64"/>
-    <cellStyle name="Normal 17" xfId="65"/>
-    <cellStyle name="Normal 2" xfId="2"/>
-    <cellStyle name="Normal 2 2" xfId="67"/>
-    <cellStyle name="Normal 2 2 2" xfId="68"/>
-    <cellStyle name="Normal 2 2 3" xfId="69"/>
-    <cellStyle name="Normal 2 3" xfId="70"/>
-    <cellStyle name="Normal 2 3 2" xfId="71"/>
-    <cellStyle name="Normal 2 3 3" xfId="72"/>
-    <cellStyle name="Normal 2 4" xfId="73"/>
-    <cellStyle name="Normal 2 5" xfId="74"/>
-    <cellStyle name="Normal 2 6" xfId="66"/>
-    <cellStyle name="Normal 3" xfId="1"/>
-    <cellStyle name="Normal 3 2" xfId="76"/>
-    <cellStyle name="Normal 3 3" xfId="77"/>
-    <cellStyle name="Normal 3 4" xfId="75"/>
-    <cellStyle name="Normal 4" xfId="78"/>
-    <cellStyle name="Normal 4 2" xfId="79"/>
-    <cellStyle name="Normal 4 3" xfId="80"/>
-    <cellStyle name="Normal 5" xfId="81"/>
-    <cellStyle name="Normal 6" xfId="82"/>
-    <cellStyle name="Normal 6 2" xfId="83"/>
-    <cellStyle name="Normal 6 3" xfId="84"/>
-    <cellStyle name="Normal 7" xfId="85"/>
-    <cellStyle name="Normal 7 2" xfId="86"/>
-    <cellStyle name="Normal 7 2 2" xfId="87"/>
-    <cellStyle name="Normal 7 2 3" xfId="88"/>
-    <cellStyle name="Normal 7 3" xfId="89"/>
-    <cellStyle name="Normal 7 3 2" xfId="90"/>
-    <cellStyle name="Normal 7 3 3" xfId="91"/>
-    <cellStyle name="Normal 7 4" xfId="92"/>
-    <cellStyle name="Normal 7 5" xfId="93"/>
-    <cellStyle name="Normal 8" xfId="94"/>
-    <cellStyle name="Normal 8 2" xfId="95"/>
-    <cellStyle name="Normal 8 2 2" xfId="96"/>
-    <cellStyle name="Normal 8 2 3" xfId="97"/>
-    <cellStyle name="Normal 8 3" xfId="98"/>
-    <cellStyle name="Normal 8 4" xfId="99"/>
-    <cellStyle name="Normal 9" xfId="100"/>
-    <cellStyle name="Normal 9 2" xfId="101"/>
-    <cellStyle name="Normal 9 2 2" xfId="102"/>
-    <cellStyle name="Normal 9 2 3" xfId="103"/>
-    <cellStyle name="Normal 9 3" xfId="104"/>
-    <cellStyle name="Normal 9 4" xfId="105"/>
-    <cellStyle name="Note 2" xfId="106"/>
-    <cellStyle name="Notiz 2" xfId="113"/>
-    <cellStyle name="Output 2" xfId="107"/>
-    <cellStyle name="Standaard_Business_List" xfId="108"/>
+    <cellStyle name="20% - Accent1 2" xfId="4" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
+    <cellStyle name="20% - Accent2 2" xfId="5" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="20% - Accent3 2" xfId="6" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
+    <cellStyle name="20% - Accent4 2" xfId="7" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
+    <cellStyle name="20% - Accent5 2" xfId="8" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
+    <cellStyle name="20% - Accent6 2" xfId="9" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
+    <cellStyle name="40% - Accent1 2" xfId="10" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
+    <cellStyle name="40% - Accent2 2" xfId="11" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
+    <cellStyle name="40% - Accent3 2" xfId="12" xr:uid="{00000000-0005-0000-0000-000008000000}"/>
+    <cellStyle name="40% - Accent4 2" xfId="13" xr:uid="{00000000-0005-0000-0000-000009000000}"/>
+    <cellStyle name="40% - Accent5 2" xfId="14" xr:uid="{00000000-0005-0000-0000-00000A000000}"/>
+    <cellStyle name="40% - Accent6 2" xfId="15" xr:uid="{00000000-0005-0000-0000-00000B000000}"/>
+    <cellStyle name="60% - Accent1 2" xfId="16" xr:uid="{00000000-0005-0000-0000-00000C000000}"/>
+    <cellStyle name="60% - Accent2 2" xfId="17" xr:uid="{00000000-0005-0000-0000-00000D000000}"/>
+    <cellStyle name="60% - Accent3 2" xfId="18" xr:uid="{00000000-0005-0000-0000-00000E000000}"/>
+    <cellStyle name="60% - Accent4 2" xfId="19" xr:uid="{00000000-0005-0000-0000-00000F000000}"/>
+    <cellStyle name="60% - Accent5 2" xfId="20" xr:uid="{00000000-0005-0000-0000-000010000000}"/>
+    <cellStyle name="60% - Accent6 2" xfId="21" xr:uid="{00000000-0005-0000-0000-000011000000}"/>
+    <cellStyle name="Accent1 2" xfId="22" xr:uid="{00000000-0005-0000-0000-000012000000}"/>
+    <cellStyle name="Accent2 2" xfId="23" xr:uid="{00000000-0005-0000-0000-000013000000}"/>
+    <cellStyle name="Accent3 2" xfId="24" xr:uid="{00000000-0005-0000-0000-000014000000}"/>
+    <cellStyle name="Accent4 2" xfId="25" xr:uid="{00000000-0005-0000-0000-000015000000}"/>
+    <cellStyle name="Accent5 2" xfId="26" xr:uid="{00000000-0005-0000-0000-000016000000}"/>
+    <cellStyle name="Accent6 2" xfId="27" xr:uid="{00000000-0005-0000-0000-000017000000}"/>
+    <cellStyle name="Bad 2" xfId="28" xr:uid="{00000000-0005-0000-0000-000018000000}"/>
+    <cellStyle name="Calculation 2" xfId="29" xr:uid="{00000000-0005-0000-0000-000019000000}"/>
+    <cellStyle name="Check Cell 2" xfId="30" xr:uid="{00000000-0005-0000-0000-00001A000000}"/>
+    <cellStyle name="Explanatory Text 2" xfId="31" xr:uid="{00000000-0005-0000-0000-00001B000000}"/>
+    <cellStyle name="Good 2" xfId="32" xr:uid="{00000000-0005-0000-0000-00001C000000}"/>
+    <cellStyle name="Heading 1 2" xfId="33" xr:uid="{00000000-0005-0000-0000-00001D000000}"/>
+    <cellStyle name="Heading 2 2" xfId="34" xr:uid="{00000000-0005-0000-0000-00001E000000}"/>
+    <cellStyle name="Heading 3 2" xfId="35" xr:uid="{00000000-0005-0000-0000-00001F000000}"/>
+    <cellStyle name="Heading 4 2" xfId="36" xr:uid="{00000000-0005-0000-0000-000020000000}"/>
+    <cellStyle name="Input 2" xfId="37" xr:uid="{00000000-0005-0000-0000-000021000000}"/>
+    <cellStyle name="Linked Cell 2" xfId="38" xr:uid="{00000000-0005-0000-0000-000022000000}"/>
+    <cellStyle name="Neutral 2" xfId="39" xr:uid="{00000000-0005-0000-0000-000023000000}"/>
+    <cellStyle name="Normal 10" xfId="40" xr:uid="{00000000-0005-0000-0000-000024000000}"/>
+    <cellStyle name="Normal 10 2" xfId="41" xr:uid="{00000000-0005-0000-0000-000025000000}"/>
+    <cellStyle name="Normal 10 2 2" xfId="42" xr:uid="{00000000-0005-0000-0000-000026000000}"/>
+    <cellStyle name="Normal 10 2 3" xfId="43" xr:uid="{00000000-0005-0000-0000-000027000000}"/>
+    <cellStyle name="Normal 10 3" xfId="44" xr:uid="{00000000-0005-0000-0000-000028000000}"/>
+    <cellStyle name="Normal 10 4" xfId="45" xr:uid="{00000000-0005-0000-0000-000029000000}"/>
+    <cellStyle name="Normal 11" xfId="46" xr:uid="{00000000-0005-0000-0000-00002A000000}"/>
+    <cellStyle name="Normal 11 2" xfId="47" xr:uid="{00000000-0005-0000-0000-00002B000000}"/>
+    <cellStyle name="Normal 11 2 2" xfId="48" xr:uid="{00000000-0005-0000-0000-00002C000000}"/>
+    <cellStyle name="Normal 11 2 3" xfId="49" xr:uid="{00000000-0005-0000-0000-00002D000000}"/>
+    <cellStyle name="Normal 11 3" xfId="50" xr:uid="{00000000-0005-0000-0000-00002E000000}"/>
+    <cellStyle name="Normal 11 4" xfId="51" xr:uid="{00000000-0005-0000-0000-00002F000000}"/>
+    <cellStyle name="Normal 12" xfId="52" xr:uid="{00000000-0005-0000-0000-000030000000}"/>
+    <cellStyle name="Normal 12 2" xfId="53" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
+    <cellStyle name="Normal 12 3" xfId="54" xr:uid="{00000000-0005-0000-0000-000032000000}"/>
+    <cellStyle name="Normal 12 4" xfId="55" xr:uid="{00000000-0005-0000-0000-000033000000}"/>
+    <cellStyle name="Normal 13" xfId="56" xr:uid="{00000000-0005-0000-0000-000034000000}"/>
+    <cellStyle name="Normal 13 2" xfId="57" xr:uid="{00000000-0005-0000-0000-000035000000}"/>
+    <cellStyle name="Normal 13 3" xfId="58" xr:uid="{00000000-0005-0000-0000-000036000000}"/>
+    <cellStyle name="Normal 13 4" xfId="59" xr:uid="{00000000-0005-0000-0000-000037000000}"/>
+    <cellStyle name="Normal 14" xfId="60" xr:uid="{00000000-0005-0000-0000-000038000000}"/>
+    <cellStyle name="Normal 14 2" xfId="61" xr:uid="{00000000-0005-0000-0000-000039000000}"/>
+    <cellStyle name="Normal 15" xfId="62" xr:uid="{00000000-0005-0000-0000-00003A000000}"/>
+    <cellStyle name="Normal 15 2" xfId="63" xr:uid="{00000000-0005-0000-0000-00003B000000}"/>
+    <cellStyle name="Normal 16" xfId="64" xr:uid="{00000000-0005-0000-0000-00003C000000}"/>
+    <cellStyle name="Normal 17" xfId="65" xr:uid="{00000000-0005-0000-0000-00003D000000}"/>
+    <cellStyle name="Normal 2" xfId="2" xr:uid="{00000000-0005-0000-0000-00003E000000}"/>
+    <cellStyle name="Normal 2 2" xfId="67" xr:uid="{00000000-0005-0000-0000-00003F000000}"/>
+    <cellStyle name="Normal 2 2 2" xfId="68" xr:uid="{00000000-0005-0000-0000-000040000000}"/>
+    <cellStyle name="Normal 2 2 3" xfId="69" xr:uid="{00000000-0005-0000-0000-000041000000}"/>
+    <cellStyle name="Normal 2 3" xfId="70" xr:uid="{00000000-0005-0000-0000-000042000000}"/>
+    <cellStyle name="Normal 2 3 2" xfId="71" xr:uid="{00000000-0005-0000-0000-000043000000}"/>
+    <cellStyle name="Normal 2 3 3" xfId="72" xr:uid="{00000000-0005-0000-0000-000044000000}"/>
+    <cellStyle name="Normal 2 4" xfId="73" xr:uid="{00000000-0005-0000-0000-000045000000}"/>
+    <cellStyle name="Normal 2 5" xfId="74" xr:uid="{00000000-0005-0000-0000-000046000000}"/>
+    <cellStyle name="Normal 2 6" xfId="66" xr:uid="{00000000-0005-0000-0000-000047000000}"/>
+    <cellStyle name="Normal 3" xfId="1" xr:uid="{00000000-0005-0000-0000-000048000000}"/>
+    <cellStyle name="Normal 3 2" xfId="76" xr:uid="{00000000-0005-0000-0000-000049000000}"/>
+    <cellStyle name="Normal 3 3" xfId="77" xr:uid="{00000000-0005-0000-0000-00004A000000}"/>
+    <cellStyle name="Normal 3 4" xfId="75" xr:uid="{00000000-0005-0000-0000-00004B000000}"/>
+    <cellStyle name="Normal 4" xfId="78" xr:uid="{00000000-0005-0000-0000-00004C000000}"/>
+    <cellStyle name="Normal 4 2" xfId="79" xr:uid="{00000000-0005-0000-0000-00004D000000}"/>
+    <cellStyle name="Normal 4 3" xfId="80" xr:uid="{00000000-0005-0000-0000-00004E000000}"/>
+    <cellStyle name="Normal 5" xfId="81" xr:uid="{00000000-0005-0000-0000-00004F000000}"/>
+    <cellStyle name="Normal 6" xfId="82" xr:uid="{00000000-0005-0000-0000-000050000000}"/>
+    <cellStyle name="Normal 6 2" xfId="83" xr:uid="{00000000-0005-0000-0000-000051000000}"/>
+    <cellStyle name="Normal 6 3" xfId="84" xr:uid="{00000000-0005-0000-0000-000052000000}"/>
+    <cellStyle name="Normal 7" xfId="85" xr:uid="{00000000-0005-0000-0000-000053000000}"/>
+    <cellStyle name="Normal 7 2" xfId="86" xr:uid="{00000000-0005-0000-0000-000054000000}"/>
+    <cellStyle name="Normal 7 2 2" xfId="87" xr:uid="{00000000-0005-0000-0000-000055000000}"/>
+    <cellStyle name="Normal 7 2 3" xfId="88" xr:uid="{00000000-0005-0000-0000-000056000000}"/>
+    <cellStyle name="Normal 7 3" xfId="89" xr:uid="{00000000-0005-0000-0000-000057000000}"/>
+    <cellStyle name="Normal 7 3 2" xfId="90" xr:uid="{00000000-0005-0000-0000-000058000000}"/>
+    <cellStyle name="Normal 7 3 3" xfId="91" xr:uid="{00000000-0005-0000-0000-000059000000}"/>
+    <cellStyle name="Normal 7 4" xfId="92" xr:uid="{00000000-0005-0000-0000-00005A000000}"/>
+    <cellStyle name="Normal 7 5" xfId="93" xr:uid="{00000000-0005-0000-0000-00005B000000}"/>
+    <cellStyle name="Normal 8" xfId="94" xr:uid="{00000000-0005-0000-0000-00005C000000}"/>
+    <cellStyle name="Normal 8 2" xfId="95" xr:uid="{00000000-0005-0000-0000-00005D000000}"/>
+    <cellStyle name="Normal 8 2 2" xfId="96" xr:uid="{00000000-0005-0000-0000-00005E000000}"/>
+    <cellStyle name="Normal 8 2 3" xfId="97" xr:uid="{00000000-0005-0000-0000-00005F000000}"/>
+    <cellStyle name="Normal 8 3" xfId="98" xr:uid="{00000000-0005-0000-0000-000060000000}"/>
+    <cellStyle name="Normal 8 4" xfId="99" xr:uid="{00000000-0005-0000-0000-000061000000}"/>
+    <cellStyle name="Normal 9" xfId="100" xr:uid="{00000000-0005-0000-0000-000062000000}"/>
+    <cellStyle name="Normal 9 2" xfId="101" xr:uid="{00000000-0005-0000-0000-000063000000}"/>
+    <cellStyle name="Normal 9 2 2" xfId="102" xr:uid="{00000000-0005-0000-0000-000064000000}"/>
+    <cellStyle name="Normal 9 2 3" xfId="103" xr:uid="{00000000-0005-0000-0000-000065000000}"/>
+    <cellStyle name="Normal 9 3" xfId="104" xr:uid="{00000000-0005-0000-0000-000066000000}"/>
+    <cellStyle name="Normal 9 4" xfId="105" xr:uid="{00000000-0005-0000-0000-000067000000}"/>
+    <cellStyle name="Note 2" xfId="106" xr:uid="{00000000-0005-0000-0000-000068000000}"/>
+    <cellStyle name="Notiz 2" xfId="113" xr:uid="{00000000-0005-0000-0000-000069000000}"/>
+    <cellStyle name="Output 2" xfId="107" xr:uid="{00000000-0005-0000-0000-00006A000000}"/>
+    <cellStyle name="Standaard_Business_List" xfId="108" xr:uid="{00000000-0005-0000-0000-00006B000000}"/>
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
-    <cellStyle name="Standard 2" xfId="3"/>
-    <cellStyle name="Standard 3" xfId="112"/>
-    <cellStyle name="Title 2" xfId="109"/>
-    <cellStyle name="Total 2" xfId="110"/>
-    <cellStyle name="Warning Text 2" xfId="111"/>
+    <cellStyle name="Standard 2" xfId="3" xr:uid="{00000000-0005-0000-0000-00006D000000}"/>
+    <cellStyle name="Standard 3" xfId="112" xr:uid="{00000000-0005-0000-0000-00006E000000}"/>
+    <cellStyle name="Title 2" xfId="109" xr:uid="{00000000-0005-0000-0000-00006F000000}"/>
+    <cellStyle name="Total 2" xfId="110" xr:uid="{00000000-0005-0000-0000-000070000000}"/>
+    <cellStyle name="Warning Text 2" xfId="111" xr:uid="{00000000-0005-0000-0000-000071000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
@@ -1539,14 +1551,17 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Larissa">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
-    <a:clrScheme name="Larissa">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1584,9 +1599,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Larissa">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1619,9 +1634,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1654,9 +1686,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Larissa">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1829,30 +1878,30 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q105"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.3984375" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="30" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="17.796875" style="7" customWidth="1"/>
-    <col min="2" max="2" width="22.59765625" style="7" customWidth="1"/>
-    <col min="3" max="3" width="12.46484375" style="7" customWidth="1"/>
-    <col min="4" max="4" width="12.59765625" style="7" customWidth="1"/>
-    <col min="5" max="5" width="11.53125" style="7" customWidth="1"/>
-    <col min="6" max="6" width="5.53125" style="21" customWidth="1"/>
-    <col min="7" max="7" width="6.1328125" style="21" customWidth="1"/>
-    <col min="8" max="8" width="5.796875" style="21" customWidth="1"/>
-    <col min="9" max="9" width="11.265625" style="7" customWidth="1"/>
-    <col min="10" max="10" width="21.265625" style="7" customWidth="1"/>
-    <col min="11" max="11" width="34.59765625" style="7" customWidth="1"/>
-    <col min="12" max="12" width="8.33203125" style="7" customWidth="1"/>
-    <col min="13" max="13" width="19.33203125" style="7" customWidth="1"/>
-    <col min="14" max="16384" width="11.3984375" style="7"/>
+    <col min="1" max="1" width="17.85546875" style="7" customWidth="1"/>
+    <col min="2" max="2" width="22.5703125" style="7" customWidth="1"/>
+    <col min="3" max="3" width="12.42578125" style="7" customWidth="1"/>
+    <col min="4" max="4" width="12.5703125" style="7" customWidth="1"/>
+    <col min="5" max="5" width="11.5703125" style="7" customWidth="1"/>
+    <col min="6" max="6" width="5.5703125" style="21" customWidth="1"/>
+    <col min="7" max="7" width="6.140625" style="21" customWidth="1"/>
+    <col min="8" max="8" width="5.85546875" style="21" customWidth="1"/>
+    <col min="9" max="9" width="11.28515625" style="7" customWidth="1"/>
+    <col min="10" max="10" width="21.28515625" style="7" customWidth="1"/>
+    <col min="11" max="11" width="34.5703125" style="7" customWidth="1"/>
+    <col min="12" max="12" width="8.28515625" style="7" customWidth="1"/>
+    <col min="13" max="13" width="19.28515625" style="7" customWidth="1"/>
+    <col min="14" max="16384" width="11.42578125" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="32" customFormat="1" ht="15.4" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:17" s="32" customFormat="1" ht="16.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="35" t="s">
         <v>29</v>
       </c>
@@ -1873,7 +1922,7 @@
       <c r="P1" s="31"/>
       <c r="Q1" s="31"/>
     </row>
-    <row r="2" spans="1:17" s="34" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:17" s="34" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="45" t="s">
         <v>30</v>
       </c>
@@ -1894,7 +1943,7 @@
       <c r="P2" s="33"/>
       <c r="Q2" s="33"/>
     </row>
-    <row r="3" spans="1:17" s="8" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:17" s="8" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="56" t="s">
         <v>3</v>
       </c>
@@ -1911,7 +1960,7 @@
       <c r="L3" s="57"/>
       <c r="M3" s="57"/>
     </row>
-    <row r="4" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="69" t="s">
         <v>19</v>
       </c>
@@ -1938,7 +1987,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="30.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:17" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="67"/>
       <c r="B5" s="49" t="s">
         <v>20</v>
@@ -1971,7 +2020,7 @@
       </c>
       <c r="M5" s="72"/>
     </row>
-    <row r="6" spans="1:17" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:17" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="70"/>
       <c r="B6" s="50"/>
       <c r="C6" s="50"/>
@@ -1992,7 +2041,7 @@
       <c r="L6" s="48"/>
       <c r="M6" s="73"/>
     </row>
-    <row r="7" spans="1:17" s="8" customFormat="1" ht="12.85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:17" s="8" customFormat="1" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="9" t="s">
         <v>19</v>
       </c>
@@ -2009,7 +2058,7 @@
       <c r="L7" s="12"/>
       <c r="M7" s="13"/>
     </row>
-    <row r="8" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="28" t="s">
         <v>15</v>
       </c>
@@ -2024,7 +2073,7 @@
       <c r="K8" s="15"/>
       <c r="L8" s="15"/>
     </row>
-    <row r="9" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="14" t="s">
         <v>8</v>
       </c>
@@ -2039,7 +2088,7 @@
       <c r="K9" s="15"/>
       <c r="L9" s="15"/>
     </row>
-    <row r="10" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="14" t="s">
         <v>9</v>
       </c>
@@ -2054,7 +2103,7 @@
       <c r="K10" s="15"/>
       <c r="L10" s="15"/>
     </row>
-    <row r="11" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="14" t="s">
         <v>16</v>
       </c>
@@ -2069,7 +2118,7 @@
       <c r="K11" s="15"/>
       <c r="L11" s="15"/>
     </row>
-    <row r="12" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="14" t="s">
         <v>10</v>
       </c>
@@ -2084,7 +2133,7 @@
       <c r="K12" s="15"/>
       <c r="L12" s="15"/>
     </row>
-    <row r="13" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="14" t="s">
         <v>17</v>
       </c>
@@ -2099,7 +2148,7 @@
       <c r="K13" s="15"/>
       <c r="L13" s="15"/>
     </row>
-    <row r="14" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="14" t="s">
         <v>31</v>
       </c>
@@ -2114,7 +2163,7 @@
       <c r="K14" s="15"/>
       <c r="L14" s="15"/>
     </row>
-    <row r="15" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="58" t="s">
         <v>26</v>
       </c>
@@ -2131,7 +2180,7 @@
       <c r="L15" s="59"/>
       <c r="M15" s="60"/>
     </row>
-    <row r="16" spans="1:17" s="16" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:17" s="16" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="67" t="s">
         <v>18</v>
       </c>
@@ -2158,7 +2207,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="17" spans="1:13" s="16" customFormat="1" ht="36.4" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:13" s="16" customFormat="1" ht="36.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="67"/>
       <c r="B17" s="51" t="s">
         <v>20</v>
@@ -2191,7 +2240,7 @@
       </c>
       <c r="M17" s="65"/>
     </row>
-    <row r="18" spans="1:13" s="16" customFormat="1" ht="36.4" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:13" s="16" customFormat="1" ht="36.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="68"/>
       <c r="B18" s="48"/>
       <c r="C18" s="48"/>
@@ -2212,7 +2261,7 @@
       <c r="L18" s="48"/>
       <c r="M18" s="66"/>
     </row>
-    <row r="19" spans="1:13" ht="12.85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:13" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="3"/>
       <c r="B19" s="1"/>
       <c r="C19" s="2"/>
@@ -2227,7 +2276,7 @@
       <c r="L19" s="6"/>
       <c r="M19" s="13"/>
     </row>
-    <row r="20" spans="1:13" ht="12.85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:13" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="3"/>
       <c r="B20" s="1"/>
       <c r="C20" s="2"/>
@@ -2242,7 +2291,7 @@
       <c r="L20" s="17"/>
       <c r="M20" s="13"/>
     </row>
-    <row r="21" spans="1:13" ht="12.85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:13" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="3"/>
       <c r="B21" s="1"/>
       <c r="C21" s="2"/>
@@ -2257,7 +2306,7 @@
       <c r="L21" s="17"/>
       <c r="M21" s="13"/>
     </row>
-    <row r="22" spans="1:13" ht="12.85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:13" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="3"/>
       <c r="B22" s="1"/>
       <c r="C22" s="2"/>
@@ -2272,7 +2321,7 @@
       <c r="L22" s="17"/>
       <c r="M22" s="13"/>
     </row>
-    <row r="23" spans="1:13" ht="12.85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:13" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="3"/>
       <c r="B23" s="1"/>
       <c r="C23" s="2"/>
@@ -2287,7 +2336,7 @@
       <c r="L23" s="17"/>
       <c r="M23" s="13"/>
     </row>
-    <row r="24" spans="1:13" ht="12.85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:13" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="3"/>
       <c r="B24" s="1"/>
       <c r="C24" s="2"/>
@@ -2302,7 +2351,7 @@
       <c r="L24" s="17"/>
       <c r="M24" s="13"/>
     </row>
-    <row r="25" spans="1:13" ht="12.85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:13" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="3"/>
       <c r="B25" s="1"/>
       <c r="C25" s="2"/>
@@ -2317,7 +2366,7 @@
       <c r="L25" s="17"/>
       <c r="M25" s="13"/>
     </row>
-    <row r="26" spans="1:13" ht="12.85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:13" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="3"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -2332,7 +2381,7 @@
       <c r="L26" s="17"/>
       <c r="M26" s="13"/>
     </row>
-    <row r="27" spans="1:13" ht="12.85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:13" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="3"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -2347,7 +2396,7 @@
       <c r="L27" s="17"/>
       <c r="M27" s="13"/>
     </row>
-    <row r="28" spans="1:13" ht="12.85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:13" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="3"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -2362,7 +2411,7 @@
       <c r="L28" s="17"/>
       <c r="M28" s="13"/>
     </row>
-    <row r="29" spans="1:13" ht="12.85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:13" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="3"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -2377,7 +2426,7 @@
       <c r="L29" s="17"/>
       <c r="M29" s="13"/>
     </row>
-    <row r="30" spans="1:13" ht="12.85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:13" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="3"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -2392,7 +2441,7 @@
       <c r="L30" s="17"/>
       <c r="M30" s="13"/>
     </row>
-    <row r="31" spans="1:13" ht="12.85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:13" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="3"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -2407,7 +2456,7 @@
       <c r="L31" s="17"/>
       <c r="M31" s="13"/>
     </row>
-    <row r="32" spans="1:13" ht="12.85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:13" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="3"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -2422,7 +2471,7 @@
       <c r="L32" s="17"/>
       <c r="M32" s="13"/>
     </row>
-    <row r="33" spans="1:13" ht="12.85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:13" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="3"/>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
@@ -2437,7 +2486,7 @@
       <c r="L33" s="17"/>
       <c r="M33" s="13"/>
     </row>
-    <row r="34" spans="1:13" ht="12.85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:13" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="3"/>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
@@ -2452,7 +2501,7 @@
       <c r="L34" s="17"/>
       <c r="M34" s="13"/>
     </row>
-    <row r="35" spans="1:13" ht="12.85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:13" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="3"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
@@ -2467,7 +2516,7 @@
       <c r="L35" s="17"/>
       <c r="M35" s="13"/>
     </row>
-    <row r="36" spans="1:13" ht="12.85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:13" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="3"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
@@ -2482,7 +2531,7 @@
       <c r="L36" s="17"/>
       <c r="M36" s="13"/>
     </row>
-    <row r="37" spans="1:13" ht="12.85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:13" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="3"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
@@ -2497,7 +2546,7 @@
       <c r="L37" s="17"/>
       <c r="M37" s="13"/>
     </row>
-    <row r="38" spans="1:13" ht="12.85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:13" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="3"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
@@ -2512,7 +2561,7 @@
       <c r="L38" s="17"/>
       <c r="M38" s="13"/>
     </row>
-    <row r="39" spans="1:13" ht="12.85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:13" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="3"/>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
@@ -2527,7 +2576,7 @@
       <c r="L39" s="17"/>
       <c r="M39" s="13"/>
     </row>
-    <row r="40" spans="1:13" ht="12.85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:13" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="3"/>
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
@@ -2542,7 +2591,7 @@
       <c r="L40" s="17"/>
       <c r="M40" s="13"/>
     </row>
-    <row r="41" spans="1:13" ht="12.85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:13" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="3"/>
       <c r="B41" s="1"/>
       <c r="C41" s="1"/>
@@ -2557,7 +2606,7 @@
       <c r="L41" s="17"/>
       <c r="M41" s="13"/>
     </row>
-    <row r="42" spans="1:13" ht="12.85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:13" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="3"/>
       <c r="B42" s="1"/>
       <c r="C42" s="1"/>
@@ -2572,7 +2621,7 @@
       <c r="L42" s="17"/>
       <c r="M42" s="13"/>
     </row>
-    <row r="43" spans="1:13" ht="12.85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:13" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="3"/>
       <c r="B43" s="1"/>
       <c r="C43" s="1"/>
@@ -2587,7 +2636,7 @@
       <c r="L43" s="17"/>
       <c r="M43" s="13"/>
     </row>
-    <row r="44" spans="1:13" ht="12.85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:13" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="3"/>
       <c r="B44" s="1"/>
       <c r="C44" s="1"/>
@@ -2602,7 +2651,7 @@
       <c r="L44" s="17"/>
       <c r="M44" s="13"/>
     </row>
-    <row r="45" spans="1:13" ht="12.85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:13" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="3"/>
       <c r="B45" s="1"/>
       <c r="C45" s="1"/>
@@ -2617,7 +2666,7 @@
       <c r="L45" s="17"/>
       <c r="M45" s="13"/>
     </row>
-    <row r="46" spans="1:13" ht="12.85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:13" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="3"/>
       <c r="B46" s="1"/>
       <c r="C46" s="1"/>
@@ -2632,7 +2681,7 @@
       <c r="L46" s="17"/>
       <c r="M46" s="13"/>
     </row>
-    <row r="47" spans="1:13" ht="12.85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:13" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="3"/>
       <c r="B47" s="1"/>
       <c r="C47" s="1"/>
@@ -2647,7 +2696,7 @@
       <c r="L47" s="17"/>
       <c r="M47" s="13"/>
     </row>
-    <row r="48" spans="1:13" ht="12.85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:13" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="3"/>
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
@@ -2662,7 +2711,7 @@
       <c r="L48" s="17"/>
       <c r="M48" s="13"/>
     </row>
-    <row r="49" spans="1:13" ht="12.85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:13" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="3"/>
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
@@ -2677,7 +2726,7 @@
       <c r="L49" s="17"/>
       <c r="M49" s="13"/>
     </row>
-    <row r="50" spans="1:13" ht="12.85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:13" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="3"/>
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
@@ -2692,7 +2741,7 @@
       <c r="L50" s="17"/>
       <c r="M50" s="13"/>
     </row>
-    <row r="51" spans="1:13" ht="12.85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:13" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="3"/>
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
@@ -2707,7 +2756,7 @@
       <c r="L51" s="17"/>
       <c r="M51" s="13"/>
     </row>
-    <row r="52" spans="1:13" ht="12.85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:13" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="3"/>
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
@@ -2722,7 +2771,7 @@
       <c r="L52" s="17"/>
       <c r="M52" s="13"/>
     </row>
-    <row r="53" spans="1:13" ht="12.85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:13" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="3"/>
       <c r="B53" s="1"/>
       <c r="C53" s="1"/>
@@ -2737,7 +2786,7 @@
       <c r="L53" s="17"/>
       <c r="M53" s="13"/>
     </row>
-    <row r="54" spans="1:13" ht="12.85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:13" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="3"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
@@ -2752,7 +2801,7 @@
       <c r="L54" s="17"/>
       <c r="M54" s="13"/>
     </row>
-    <row r="55" spans="1:13" ht="12.85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:13" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="3"/>
       <c r="B55" s="1"/>
       <c r="C55" s="1"/>
@@ -2767,7 +2816,7 @@
       <c r="L55" s="17"/>
       <c r="M55" s="13"/>
     </row>
-    <row r="56" spans="1:13" ht="12.85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:13" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="3"/>
       <c r="B56" s="1"/>
       <c r="C56" s="1"/>
@@ -2782,7 +2831,7 @@
       <c r="L56" s="17"/>
       <c r="M56" s="13"/>
     </row>
-    <row r="57" spans="1:13" ht="12.85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:13" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="3"/>
       <c r="B57" s="1"/>
       <c r="C57" s="1"/>
@@ -2797,7 +2846,7 @@
       <c r="L57" s="17"/>
       <c r="M57" s="13"/>
     </row>
-    <row r="58" spans="1:13" ht="12.85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:13" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="3"/>
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
@@ -2812,7 +2861,7 @@
       <c r="L58" s="17"/>
       <c r="M58" s="13"/>
     </row>
-    <row r="59" spans="1:13" ht="12.85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:13" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="3"/>
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
@@ -2827,7 +2876,7 @@
       <c r="L59" s="17"/>
       <c r="M59" s="13"/>
     </row>
-    <row r="60" spans="1:13" ht="12.85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:13" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="3"/>
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
@@ -2842,7 +2891,7 @@
       <c r="L60" s="17"/>
       <c r="M60" s="13"/>
     </row>
-    <row r="61" spans="1:13" ht="12.85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:13" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="3"/>
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
@@ -2857,7 +2906,7 @@
       <c r="L61" s="17"/>
       <c r="M61" s="13"/>
     </row>
-    <row r="62" spans="1:13" ht="12.85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:13" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="3"/>
       <c r="B62" s="1"/>
       <c r="C62" s="1"/>
@@ -2872,7 +2921,7 @@
       <c r="L62" s="17"/>
       <c r="M62" s="13"/>
     </row>
-    <row r="63" spans="1:13" ht="12.85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:13" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="3"/>
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
@@ -2887,7 +2936,7 @@
       <c r="L63" s="17"/>
       <c r="M63" s="13"/>
     </row>
-    <row r="64" spans="1:13" ht="12.85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:13" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="3"/>
       <c r="B64" s="1"/>
       <c r="C64" s="1"/>
@@ -2902,7 +2951,7 @@
       <c r="L64" s="17"/>
       <c r="M64" s="13"/>
     </row>
-    <row r="65" spans="1:13" ht="12.85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:13" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="3"/>
       <c r="B65" s="1"/>
       <c r="C65" s="1"/>
@@ -2917,7 +2966,7 @@
       <c r="L65" s="17"/>
       <c r="M65" s="13"/>
     </row>
-    <row r="66" spans="1:13" ht="12.85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:13" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="3"/>
       <c r="B66" s="1"/>
       <c r="C66" s="1"/>
@@ -2932,7 +2981,7 @@
       <c r="L66" s="17"/>
       <c r="M66" s="13"/>
     </row>
-    <row r="67" spans="1:13" ht="12.85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:13" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="3"/>
       <c r="B67" s="1"/>
       <c r="C67" s="1"/>
@@ -2947,7 +2996,7 @@
       <c r="L67" s="17"/>
       <c r="M67" s="13"/>
     </row>
-    <row r="68" spans="1:13" ht="12.85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:13" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="3"/>
       <c r="B68" s="1"/>
       <c r="C68" s="1"/>
@@ -2962,7 +3011,7 @@
       <c r="L68" s="17"/>
       <c r="M68" s="13"/>
     </row>
-    <row r="69" spans="1:13" ht="12.85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:13" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="3"/>
       <c r="B69" s="1"/>
       <c r="C69" s="1"/>
@@ -2977,7 +3026,7 @@
       <c r="L69" s="17"/>
       <c r="M69" s="13"/>
     </row>
-    <row r="70" spans="1:13" ht="12.85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:13" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="3"/>
       <c r="B70" s="1"/>
       <c r="C70" s="1"/>
@@ -2992,7 +3041,7 @@
       <c r="L70" s="17"/>
       <c r="M70" s="13"/>
     </row>
-    <row r="71" spans="1:13" ht="12.85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:13" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="3"/>
       <c r="B71" s="1"/>
       <c r="C71" s="1"/>
@@ -3007,7 +3056,7 @@
       <c r="L71" s="17"/>
       <c r="M71" s="13"/>
     </row>
-    <row r="72" spans="1:13" ht="12.85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:13" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="3"/>
       <c r="B72" s="1"/>
       <c r="C72" s="1"/>
@@ -3022,7 +3071,7 @@
       <c r="L72" s="17"/>
       <c r="M72" s="13"/>
     </row>
-    <row r="73" spans="1:13" ht="12.85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:13" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="3"/>
       <c r="B73" s="1"/>
       <c r="C73" s="1"/>
@@ -3037,7 +3086,7 @@
       <c r="L73" s="17"/>
       <c r="M73" s="13"/>
     </row>
-    <row r="74" spans="1:13" ht="12.85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:13" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="3"/>
       <c r="B74" s="1"/>
       <c r="C74" s="1"/>
@@ -3052,7 +3101,7 @@
       <c r="L74" s="17"/>
       <c r="M74" s="13"/>
     </row>
-    <row r="75" spans="1:13" ht="12.85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:13" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="3"/>
       <c r="B75" s="1"/>
       <c r="C75" s="1"/>
@@ -3067,7 +3116,7 @@
       <c r="L75" s="17"/>
       <c r="M75" s="13"/>
     </row>
-    <row r="76" spans="1:13" ht="12.85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:13" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="3"/>
       <c r="B76" s="1"/>
       <c r="C76" s="1"/>
@@ -3082,7 +3131,7 @@
       <c r="L76" s="17"/>
       <c r="M76" s="13"/>
     </row>
-    <row r="77" spans="1:13" ht="12.85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:13" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="3"/>
       <c r="B77" s="1"/>
       <c r="C77" s="1"/>
@@ -3097,7 +3146,7 @@
       <c r="L77" s="17"/>
       <c r="M77" s="13"/>
     </row>
-    <row r="78" spans="1:13" ht="12.85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:13" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="3"/>
       <c r="B78" s="1"/>
       <c r="C78" s="1"/>
@@ -3112,7 +3161,7 @@
       <c r="L78" s="17"/>
       <c r="M78" s="13"/>
     </row>
-    <row r="79" spans="1:13" ht="12.85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:13" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="3"/>
       <c r="B79" s="1"/>
       <c r="C79" s="1"/>
@@ -3127,7 +3176,7 @@
       <c r="L79" s="17"/>
       <c r="M79" s="13"/>
     </row>
-    <row r="80" spans="1:13" ht="12.85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:13" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="3"/>
       <c r="B80" s="1"/>
       <c r="C80" s="1"/>
@@ -3142,7 +3191,7 @@
       <c r="L80" s="17"/>
       <c r="M80" s="13"/>
     </row>
-    <row r="81" spans="1:13" ht="12.85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:13" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="3"/>
       <c r="B81" s="1"/>
       <c r="C81" s="1"/>
@@ -3157,7 +3206,7 @@
       <c r="L81" s="17"/>
       <c r="M81" s="13"/>
     </row>
-    <row r="82" spans="1:13" ht="12.85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:13" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="3"/>
       <c r="B82" s="1"/>
       <c r="C82" s="1"/>
@@ -3172,7 +3221,7 @@
       <c r="L82" s="17"/>
       <c r="M82" s="13"/>
     </row>
-    <row r="83" spans="1:13" ht="12.85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:13" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="3"/>
       <c r="B83" s="1"/>
       <c r="C83" s="1"/>
@@ -3187,7 +3236,7 @@
       <c r="L83" s="17"/>
       <c r="M83" s="13"/>
     </row>
-    <row r="84" spans="1:13" ht="12.85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:13" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="3"/>
       <c r="B84" s="1"/>
       <c r="C84" s="1"/>
@@ -3202,7 +3251,7 @@
       <c r="L84" s="17"/>
       <c r="M84" s="13"/>
     </row>
-    <row r="85" spans="1:13" ht="12.85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:13" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="3"/>
       <c r="B85" s="1"/>
       <c r="C85" s="1"/>
@@ -3217,7 +3266,7 @@
       <c r="L85" s="17"/>
       <c r="M85" s="13"/>
     </row>
-    <row r="86" spans="1:13" ht="12.85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:13" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="3"/>
       <c r="B86" s="1"/>
       <c r="C86" s="1"/>
@@ -3232,7 +3281,7 @@
       <c r="L86" s="17"/>
       <c r="M86" s="13"/>
     </row>
-    <row r="87" spans="1:13" ht="12.85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:13" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="3"/>
       <c r="B87" s="1"/>
       <c r="C87" s="1"/>
@@ -3247,7 +3296,7 @@
       <c r="L87" s="17"/>
       <c r="M87" s="13"/>
     </row>
-    <row r="88" spans="1:13" ht="12.85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:13" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="3"/>
       <c r="B88" s="1"/>
       <c r="C88" s="1"/>
@@ -3262,7 +3311,7 @@
       <c r="L88" s="17"/>
       <c r="M88" s="13"/>
     </row>
-    <row r="89" spans="1:13" ht="12.85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:13" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="3"/>
       <c r="B89" s="1"/>
       <c r="C89" s="1"/>
@@ -3277,7 +3326,7 @@
       <c r="L89" s="17"/>
       <c r="M89" s="13"/>
     </row>
-    <row r="90" spans="1:13" ht="12.85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:13" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="3"/>
       <c r="B90" s="1"/>
       <c r="C90" s="1"/>
@@ -3292,7 +3341,7 @@
       <c r="L90" s="17"/>
       <c r="M90" s="13"/>
     </row>
-    <row r="91" spans="1:13" ht="12.85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:13" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="3"/>
       <c r="B91" s="1"/>
       <c r="C91" s="1"/>
@@ -3307,7 +3356,7 @@
       <c r="L91" s="17"/>
       <c r="M91" s="13"/>
     </row>
-    <row r="92" spans="1:13" ht="12.85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:13" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="3"/>
       <c r="B92" s="1"/>
       <c r="C92" s="1"/>
@@ -3322,7 +3371,7 @@
       <c r="L92" s="17"/>
       <c r="M92" s="13"/>
     </row>
-    <row r="93" spans="1:13" ht="12.85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:13" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="3"/>
       <c r="B93" s="1"/>
       <c r="C93" s="1"/>
@@ -3337,7 +3386,7 @@
       <c r="L93" s="17"/>
       <c r="M93" s="13"/>
     </row>
-    <row r="94" spans="1:13" ht="12.85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:13" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="3"/>
       <c r="B94" s="1"/>
       <c r="C94" s="1"/>
@@ -3352,7 +3401,7 @@
       <c r="L94" s="17"/>
       <c r="M94" s="13"/>
     </row>
-    <row r="95" spans="1:13" ht="12.85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:13" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="3"/>
       <c r="B95" s="1"/>
       <c r="C95" s="1"/>
@@ -3367,7 +3416,7 @@
       <c r="L95" s="17"/>
       <c r="M95" s="13"/>
     </row>
-    <row r="96" spans="1:13" ht="12.85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:13" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="3"/>
       <c r="B96" s="1"/>
       <c r="C96" s="1"/>
@@ -3382,7 +3431,7 @@
       <c r="L96" s="17"/>
       <c r="M96" s="13"/>
     </row>
-    <row r="97" spans="1:13" ht="12.85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:13" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="3"/>
       <c r="B97" s="1"/>
       <c r="C97" s="1"/>
@@ -3397,7 +3446,7 @@
       <c r="L97" s="17"/>
       <c r="M97" s="13"/>
     </row>
-    <row r="98" spans="1:13" ht="12.85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:13" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="3"/>
       <c r="B98" s="1"/>
       <c r="C98" s="1"/>
@@ -3412,7 +3461,7 @@
       <c r="L98" s="17"/>
       <c r="M98" s="13"/>
     </row>
-    <row r="99" spans="1:13" ht="12.85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:13" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="3"/>
       <c r="B99" s="1"/>
       <c r="C99" s="1"/>
@@ -3427,7 +3476,7 @@
       <c r="L99" s="17"/>
       <c r="M99" s="13"/>
     </row>
-    <row r="100" spans="1:13" ht="12.85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:13" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="3"/>
       <c r="B100" s="1"/>
       <c r="C100" s="1"/>
@@ -3442,7 +3491,7 @@
       <c r="L100" s="17"/>
       <c r="M100" s="13"/>
     </row>
-    <row r="101" spans="1:13" ht="12.85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:13" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="3"/>
       <c r="B101" s="1"/>
       <c r="C101" s="1"/>
@@ -3457,7 +3506,7 @@
       <c r="L101" s="17"/>
       <c r="M101" s="13"/>
     </row>
-    <row r="102" spans="1:13" ht="12.85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:13" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="3"/>
       <c r="B102" s="1"/>
       <c r="C102" s="1"/>
@@ -3472,7 +3521,7 @@
       <c r="L102" s="17"/>
       <c r="M102" s="13"/>
     </row>
-    <row r="103" spans="1:13" ht="12.85" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:13" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="3"/>
       <c r="B103" s="1"/>
       <c r="C103" s="1"/>
@@ -3487,7 +3536,7 @@
       <c r="L103" s="17"/>
       <c r="M103" s="13"/>
     </row>
-    <row r="104" spans="1:13" ht="12.85" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:13" ht="12.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A104" s="4"/>
       <c r="B104" s="5"/>
       <c r="C104" s="5"/>
@@ -3502,7 +3551,7 @@
       <c r="L104" s="29"/>
       <c r="M104" s="13"/>
     </row>
-    <row r="105" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="K105" s="20"/>
       <c r="L105" s="20"/>
     </row>
@@ -3546,16 +3595,16 @@
     <mergeCell ref="L1:M1"/>
     <mergeCell ref="A2:M2"/>
   </mergeCells>
-  <dataValidations count="3">
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F3:F1048576">
+  <dataValidations disablePrompts="1" count="3">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F3:F1048576" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>1</formula1>
       <formula2>31</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G3:G1048576">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G3:G1048576" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>1</formula1>
       <formula2>12</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3:H1048576">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3:H1048576" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>1900</formula1>
       <formula2>2100</formula2>
     </dataValidation>
